--- a/260415_AI_공공조달_RFP_분석_v3.xlsx
+++ b/260415_AI_공공조달_RFP_분석_v3.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -571,52 +571,31 @@
           <t>기본 정보</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
       <c r="H1" s="3" t="inlineStr">
         <is>
           <t>사업 규모 및 조건</t>
         </is>
       </c>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-      <c r="M1" s="4" t="n"/>
-      <c r="N1" s="4" t="n"/>
       <c r="O1" s="5" t="inlineStr">
         <is>
           <t>AI/기술 핵심</t>
         </is>
       </c>
-      <c r="P1" s="6" t="n"/>
-      <c r="Q1" s="6" t="n"/>
-      <c r="R1" s="6" t="n"/>
       <c r="S1" s="7" t="inlineStr">
         <is>
           <t>과업 내용</t>
         </is>
       </c>
-      <c r="T1" s="8" t="n"/>
       <c r="U1" s="9" t="inlineStr">
         <is>
           <t>산출물·법령</t>
         </is>
       </c>
-      <c r="V1" s="10" t="n"/>
       <c r="W1" s="11" t="inlineStr">
         <is>
           <t>AX 혁신 인사이트</t>
         </is>
       </c>
-      <c r="X1" s="12" t="n"/>
-      <c r="Y1" s="12" t="n"/>
-      <c r="Z1" s="12" t="n"/>
-      <c r="AA1" s="12" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
@@ -1529,6 +1508,409 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="400" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>RFP-006</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>부천대학교 AI기반 그룹웨어 고도화 사업</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>부천대학교</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>산학협력단</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>미기재</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>520000</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>제한경쟁입찰(협상에 의한 계약)</t>
+        </is>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="L8" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" s="19" t="inlineStr">
+        <is>
+          <t>소프트웨어사업자(컴퓨터관련서비스사업):1468 / 직접생산확인증명서(정보시스템개발서비스, 세부품명번호 8111159901)</t>
+        </is>
+      </c>
+      <c r="O8" s="19" t="inlineStr">
+        <is>
+          <t>시스템고도화</t>
+        </is>
+      </c>
+      <c r="P8" s="19" t="inlineStr">
+        <is>
+          <t>그룹웨어(전자결재·전자우편·메신저·통합검색·일정/자원관리)에 생성형 AI 및 AI Agent 기능 연계</t>
+        </is>
+      </c>
+      <c r="Q8" s="19" t="inlineStr">
+        <is>
+          <t>생성형 AI, LLM, ChatGPT, Gemini, RAG, AI Agent, MCP, AI봇, AI기안, STT(음성인식)</t>
+        </is>
+      </c>
+      <c r="R8" s="19" t="inlineStr">
+        <is>
+          <t>문서·메일 초안 작성, 요약·번역·어조변환, Q&amp;A 봇, 일정·자원 자동예약, RAG 기반 검색으로 환각 최소화, 음성 인식 기반 메시지 입력 등 업무 효율화 및 접근성 향상</t>
+        </is>
+      </c>
+      <c r="S8" s="19" t="inlineStr">
+        <is>
+          <t>【시스템장비구성】 ECR-001 구축 시스템 요구사항 / ECR-002 상용 패키지 S/W 도입
+【기능】 SFR-001 그룹웨어 기본 공통(개발방향 및 공통사항) / SFR-002 포털시스템의 메인 화면 / SFR-003 내부 전자우편 기능 / SFR-004 전자결재 기안 / SFR-005 전자결재 결재 처리 / SFR-006 전자결재 서식함 / SFR-007 전자결재 문서수발신 / SFR-008 전자결재 기록물 관리 / SFR-009 전자결재 연동 / SFR-010 게시판 관리 / SFR-012 자원관리 / SFR-012-1 일정관리 / SFR-013 문서관리 / SFR-014 설문조사 / SFR-015 근태관리 / SFR-016 조직도 / SFR-017 협업 업무 관리 / SFR-018 협업 공간 관리 / SFR-019 프로젝트 관리 / SFR-020 위키 관리 / SFR-021 그룹웨어 메신저 / SFR-022 모바일 그룹웨어 / SFR-023 사용자 환경 설정 / SFR-024 시스템 관리 기능
+【성능】 PER-001 시스템 성능요건
+【인터페이스】 SIR-001 사용자 인터페이스 / SIR-002 웹 표준 준수
+【데이터】 DAR-001 데이터 요구사항(표준화·최적화) / DAR-002 데이터 이관 / DAR-003 데이터 백업/복구
+【테스트】 TER-001 테스트 요구사항 / TER-002 승인(인수) 검사 및 테스트
+【보안】 SER-001 보안 공통사항 / SER-002 개인정보 보호 / SER-003 보안 취약점 제거
+【품질】 QUR-001 품질관리 방안 / QUR-002 기능성 / QUR-003 백업 및 복구
+【제약】 COR-001 특허권 또는 저작권 관리 / COR-002 개발표준 준수 / COR-003 성과품의 소유 / COR-004 계약 해지 및 조건
+【프로젝트관리】 PMR-001 일반사항 / PMR-002 사업수행 조직 구성 / PMR-003 산출물 검수 / PMR-004 시험운영 / PMR-005 사업보고 및 산출물 관리
+【프로젝트지원】 PSR-001 운영 및 유지관리를 위한 지원사항 / PSR-002 교육훈련 / PSR-003 기술지원</t>
+        </is>
+      </c>
+      <c r="T8" s="19" t="inlineStr">
+        <is>
+          <t>ECR-001 구축 시스템 요구사항: 효율적 개발환경을 위해 별도 서버에 구축·운용 가능. 그룹웨어 운영에 최적인 서버환경 제안, 서버 구축 비용은 본 용역 외 별도 추진. S/W는 안정화된 최신 버전 사용.
+ECR-002 상용 패키지 S/W 도입: 최신 버전 설치 또는 이관, 타 시스템과의 연동·호환성 보장. 사용자 라이선스 500명 확보, 부족분은 사업자 부담. 주요 기능은 포털·전자우편·전자결재·기록물철관리·게시판·일정관리·설문조사·파일관리·문서관리·협업·통합인증·조직도 연계 등. 현 운영 그룹웨어의 주요 커스터마이징 기능 승계 및 KISA 소프트웨어 개발보안 가이드 준수.
+SFR-001 개발방향 및 공통사항: 현 시스템 성능·기능 상회, 메일/결재/게시판/사용자정보 등 모든 데이터 이관. HTML5 반응형 UI, Edge·Chrome 등 다중 브라우저, OS/DBMS 독립. IP 기반 접속·메뉴 차단, 자동세션 종료, DB 암호화, 비밀번호 규칙(영문/숫자/특수문자 10자 이상), 모바일 생체인증 로그인, 조직도 직급표시·정렬.
+SFR-002 포털시스템의 메인 화면: 전사·부서·업무·개인별 포털 UI, 다양한 테마, 포틀릿 스킨·권한·Drag&amp;Drop, iFrame·Chart 포틀릿, 통합알림(모든 이벤트·검색·팝업·연동로그), 통합인증(SSO 8식, 무에이전트), 통합검색(게시판·메일·결재·주소록·위키 본문·첨부, 자동완성·유사어·필터·권한반영), AI 연계(ChatGPT/Gemini 기반 요약·번역·어조변환·검색, Q&amp;A 봇, 문서·메일 초안·맞춤법). 기존 포틀릿 23종·신규 15종.
+SFR-003 내부 전자우편: HTML5 반응형, 대용량·보안·예약·긴급메일, Drag&amp;Drop 첨부, 자동완성·자동저장, 발송취소·지연발송, 태그·라벨, AI 요약·답변추천, RAG 기반 검색으로 환각 최소화, 첨부 기반 AI 대화, 결재양식 자동입력, AI Agent(MCP) 일정·자원 자동등록, PC·모바일 음성인식 입력. 관리자 기능으로 POP3/IMAP 제한, 보관기간·용량 제한, 대표(Alias)·사서함 계정, 강제회수, 메일 복원, 국가코드 IP 아이콘.
+SFR-004 전자결재 기안: 아래한글 웹 기안기 및 폼 기안기(Non ActiveX), 전자정부 표준프레임워크 호환성 인증. 내부기안·발송/접수·검토·참조·열람·공람, 대리기안, 전결·대결·순차/병렬 협조, 부재설정, 사용자정보 자동입력, 임시저장, 관련문서 링크, 기록물철 지정·문서번호 자동생성, 대내외 수신처 복수지정, 양식별 고정결재선·기본 수신/참조/공람, 열람제한, 재기안, 직책별·역할별 결재선, 타 시스템 연동 API, 캡쳐이미지 첨부, 강제회수, 비전자문서 생산/접수 등록.
+SFR-005 전자결재 결재 처리: 승인·반려·반대·보류·선결·예결·결재취소. 진행상태 조회, 등록자만 열람 가능, 별도 보안결재 암호, 전자서명, 미결문서 처리, 결재완료 자동분류, 수정·결재선 변경, 접수 후 내부결재, 기안자 알림, 반려 시 의견 필수·단계별 반려, 시행문 자동발신, 원본/수정본 동시 보기, 직인 자동날인, 다수 대결자, 중간결재 순차/병렬·내부상신(이중기안), 결재유형별 부재옵션.
+SFR-006 전자결재 서식함: 전사 공용서식관리(기안·협조·대외공문), 신청양식 등록, 서식함·결재유형 설정, 웹폼/웹에디터 서식 생성, 양식 내 스크립트, 서식별 권한·프로세스, 완료문서 부서별 기록물 저장.
+SFR-007 전자결재 문서수발신: 접수·반송·회수, 대내문서 배부·담당자 지정·공람자 추가, 발송/접수 이력, 배부대장 자동등록, 대외문서 행정안전부 전자문서유통센터 연계, 발송상태(발송·도달·수신·오류·접수·재발송·반송) 조회, 수기 등록(주소·전자우편·팩스), 다수 수신처 엑셀 일괄 업로드, 반송문서 재배부.
+SFR-008 전자결재 기록물 관리: 행정업무 효율적 운영 규정 및 공공기관 기록물 관리에 관한 법률 준수. 신사무규정 기반 대·중·소·단위업무·기록물철 등록, 공통/고유 구분, 업무부서 설정, 기록물등록대장·배부대장·분류기준표 조회 및 엑셀 다운로드, 편철·분리·통합·이관·삭제/복원 이력, 관인날인대장, 다양한 조건 조회, 붙임기안·분리등록·열람제한.
+SFR-009 전자결재 연동: 기존 전자결재 데이터 마이그레이션, 일반양식/연동양식 구별, 타시스템 연동 API, 결재 상태별 인터페이스 지정, SQL/Procedure/JSON/XML 인터페이스, 기존 종합정보시스템 근태관리 연계, 오류 알림, 양식 설계 컨트롤, 결재 문서 DB화·사용자 정의 문서함, 연동로그 상세조회.
+SFR-010 게시판 관리: 검색·즐겨찾기·정렬·권한, 게시판 형식(일반·자료실·앨범), 관리자 정의 화면, 게시 기한·승인, 웹 에디터, 메일 발송, 답변 알림, 댓글 첨부·태그, 양식 사용, 템플릿 재활용, 익명·신문고·보안·예약 게시, 용량·첨부 제한, 추가 컬럼 생성.
+SFR-012 자원관리: 차량·회의실·노트북 등록, 멀티자원 예약, 예약/승인제, 일/주/월 현황, 자원별 관리자·예약시간·요일 지정, 첨부파일, 반납 자원, 참석자 알림, 예약현황 검색·통계, AI Agent(MCP) 자동 예약.
+SFR-012-1 일정관리: 목록/일간/주간/월간/연간, 캘린더 공유, 공유 요청 수락/거부, 타 사용자 일정확인, 회의실 연동, 인쇄·검색, Drag 수정, 알림(분·시·일), CalDAV 모바일 동기화, 구글/아웃룩 외부 API, 일정대리인, AI Agent(MCP) 자동 예약.
+SFR-013 문서관리: 전사 문서함 폴더 CRUD·소유자 변경, 카테고리 지정, 부서별 문서함, 공유, 권한 승계 복사, 직위·직책·사용자별 권한, 상위 권한 상속·차단, 버전관리, 이력 저장, 임시보관·폐기·복원, 보존기간 만료 자동 폐기.
+SFR-014 설문조사: 객관식·주관식·순위형·이미지형·슬라이더형·드롭다운형, 승인, 분기, 필수항목, 투표, 기간, 복사·순서 변경, 내부·메일 외부설문, 대상자 조직도 연계, 결과 공개/비공개/반공개, 엑셀저장·통계, 재사용.
+SFR-015 근태관리: 출퇴근·연장근무·근무계획표 기반 일반·시차·탄력·선택·간주·재량근무제, 연차촉진통보·사용시기 통보, GPS/WIFI 좌표 기반 원격근무지 및 반경 출퇴근 관리.
+SFR-016 조직도: 조직원·부재자·신규입사자 조회, 리스트/명함/분할형, 변동 이력, 부서겸직·대표부서 선택, 로그아웃 없이 조직변경, 전체·메뉴 관리자 지정, 정렬·직급·직책 표시, 조직개편·인사이동 자동 적용, 인사시스템 연계, 외부사용자 별도관리.
+SFR-017 협업 업무 관리: 오프라인 업무 온라인화, 개인·팀단위 업무, 화면·컬럼 추가, 다양한 컨트롤, 웹 스프레드시트, PC 엑셀 업로드·이력, 기존업무 데이터 연동, 타 시스템 API, 타임라인·댓글, 입력권한·담당자, 프로세스 설정, 목록화면, 차트, 분류·라벨, 프로젝트 모듈 연계, 업무편람 프로세스화.
+SFR-018 협업 공간 관리: 팀룸 생성·운영(자유/승인 개설), 공개·비공개, 가입 방식, 일괄 메일·쪽지, SNS 피드형 커뮤니케이션, 팀룸 내 프로젝트·업무신청·게시판·문서관리 연동, 팀 일정 공유·팀 전용 사서함.
+SFR-019 프로젝트 관리: 개인·협업 프로젝트, 진행·이슈·일감 관리, 일감 내 메일·결재 기안, 보고서, 하위 일감, 간트차트(일/주/월), 완료 잠금, 개설·사용현황.
+SFR-020 위키 관리: 주제별 페이지 공유, 트리 계층구조·하이퍼링크, 등록·수정·삭제 승인, 변경이력·복원, 업데이트 메일 공지, 편집 도구·표·이미지·동영상, 권한 관리, 전사·조직·프로젝트별 위키, 검색.
+SFR-021 그룹웨어 메신저: 설치형+임베디드, 상태정보·인사말, 그룹웨어 알림 카운터·바로가기, 알림톡 대화형 수신, 서버 저장 실시간 동기화, 1:1·1:N·수신확인, Drag&amp;Drop 파일·이미지, 화면 캡처·편집, 대화방 파일 모아보기, AI 번역·맞춤법·어조·요약·답변추천, 음성 메시지, 메일·쪽지·일정·설문 연계, 원격지원, 대화불가 시간, 보관기간 자동삭제, PC-모바일 양방향 동기화.
+SFR-022 모바일 그룹웨어: PC-모바일 실시간 동기화, 2-Factor 생체인증, 반응형 포틀릿 포탈, 스마트폰·태블릿 지원, 메뉴별 권한, GPS/WIFI 출퇴근·부재 신청, 전자결재 기안·승인·반려·전자서명, 메일·게시판·협업, Push 알림·방해금지, 연락처·캘린더 동기화.
+SFR-023 사용자 환경 설정: 개인정보·즐겨찾기·개인 포틀릿 관리, 알림·팝업 위치, 글로벌 타임, 부재 설정(대리결재자), 사용자 갤러리.
+SFR-024 시스템 관리 기능: 메뉴별 관리, 비밀번호 정책, 자동 세션 종료, 접속로그·첨부 제한, IP 허용/차단, 배너·팝업 관리, 포틀릿·탭포틀릿, 보안등급·조직도 권한, 접속·브라우저 통계, 권한 이관, 통합 알림 설정·외부 알림 연동 API, 배치 모니터링, 파일 변경 탐지·자동 격리, 관리자 UI·다중 서버 모니터링.
+PER-001 시스템 성능요건: 단순 기능 3초 이내, 성능테스트·최적화, 쿼리 지연 개선, Peak·과부하 테스트, 무중단 서비스, 장애 시 백업·복구, 확장성·호환성·유연성.
+SIR-001 사용자 인터페이스: 직관적 UI, 로딩·에러 안내, 오류 메시지의 중요정보 유출 방지, 반응형 레이아웃.
+SIR-002 웹 표준 준수: 전자정부서비스 호환성·W3C 표준, ActiveX·EXE 배제, 동작·레이아웃·플러그인 호환성, 다중 브라우저.
+DAR-001 데이터 요구사항: 행정안전부 DB 표준화 지침 준수, 기존 DB 분석·재설계·튜닝, 개인정보 암호화, 직관적 명명.
+DAR-002 데이터 이관: 조직도·사용자·개인정보·직위·직급, 게시판·결재(문서함) 본문·첨부, 전자우편·주소록 이관, 업무협조 데이터.
+DAR-003 데이터 백업/복구: 사업기간 내 백업·복구 방안, 장애·보안사고 후 즉시 복구.
+TER-001 테스트 요구사항: 시험검증 방안, 현행 시스템 무영향, 성능·보안성 점검, 다중 브라우저 테스트, 목표품질·결과서, 도구 사업자 부담, 데이터 이관 무결성·정합성, 파일 디렉토리 최적화.
+TER-002 승인(인수) 검사 및 테스트: 7일 이내 검사, 요구사항별 적합/부적합 판정, 테스트 데이터 준비, 별도 문서 승인일.
+SER-001 보안 공통사항: 인원·문서·장비 보안 계획, 보안서약서·개인정보보호 서약서·위탁 계약서, 취득 자료 외부 공개 금지, 사업종료 시 자료 보유 금지, 보안사고 시 형사처벌·손해배상.
+SER-002 개인정보 보호: 개인정보보호법·정보통신망법 준수, DB 암호화.
+SER-003 보안 취약점 제거: 보안약점 진단도구, 국정원 8대 취약점·OWASP TOP 10·행안부 지침, 웹 취약점 진단·시큐어 코딩·수동 모의해킹, HTTPS 리다이렉트.
+QUR-001 품질관리 방안: 품질보증 범위·목표·조직·절차·결과물·점검방법·도구, 단계별 활동 계획, 위험관리 계획서·결과서, 24시간 무중단, 요구사항 추적, 결함 100% 조치.
+QUR-002 기능성: 승인된 요구사항 최종 요구사항, 검증 활동, 통합·시스템 테스트 방안.
+QUR-003 백업 및 복구: 장애요소 유형별 대처방안 문서화, 마스터 환경 백업·복구, 오픈 이후 안정화·이후 백업 전략, 매뉴얼, 유실데이터 처리.
+COR-001 특허권/저작권 관리: 제3자 침해 방지, 분쟁 시 민·형사 책임, 디자인·콘텐츠·폰트 저작권법 준수.
+COR-002 개발표준 준수: 정보시스템 구축·운영 지침, SW 개발보안 가이드, 웹응용프로그램 개발보안 가이드, 호환성 준수지침, 표준개인정보보호지침, 웹 접근성 국가표준, WCAG 2.1, 개인정보 안전성 확보조치 기준, SW사업 요구사항 분석적용 가이드 준수.
+COR-003 성과품의 소유: 지적재산권은 발주기관 소유, 원시자료 사용 시 저작권 확인, 타 기관 공동활용 계획 없음.
+COR-004 계약 해지 및 조건: 사전승인 없는 양도, 착수기일 미경과, 중대한 위반, 태만·불성실 시 해지 가능, 해지 시 대가 정산, 업무 인계.
+PMR-001 일반사항: 최신 기술·신의성실, 계약 후 10일 이내 사업수행계획서 제출, 과업 일부 변경 가능, 감독관 지시, 하도급 불가, 경비 사업자 부담.
+PMR-002 사업수행 조직 구성: PM 경력자, 인력교체 제한(불가항력 시 1개월 전 승인), 부적절 인원 10일 내 교체, 핵심인력 교체 2주 전 승인·1주 이상 인수인계, 동등 이상 자격.
+PMR-003 산출물 검수: 작업진척 기준 진행검사, 시정요구 성실 이행, 프로그램별 일정 검수.
+PMR-004 시험운영: 개발서버→운영서버 이전 후 공식 오픈 전까지 운영, 모든 기능·연계 서비스 테스트.
+PMR-005 사업보고 및 산출물 관리: 세부 수행계획 제출, 수시·착수·중간·최종보고, 주간/월간 보고.
+PSR-001 운영 및 유지관리 지원: 품질·하자보증 검수일로부터 1년, 장애 접수 후 4시간 내 무상 조치, 관리자 교육·매뉴얼.
+PSR-002 교육훈련: 종합적 교육지원 방안, 사용자·관리자 매뉴얼 제공, 교육 비용 전액 제안사 부담.
+PSR-003 기술지원: 기술이전 목록·방법 계획, 실무자 참여 기술능력 배양, 지속적 정보제공·기술자문.</t>
+        </is>
+      </c>
+      <c r="U8" s="19" t="inlineStr">
+        <is>
+          <t>부천대학교 그룹웨어 시스템 업그레이드 결과물, 사용자 라이센스 500 User, 완료보고서, 관리자 매뉴얼, 사용자 매뉴얼, 보안서약서·개인정보보호 서약서·개인정보처리 위탁 계약서, 백업/복구 매뉴얼(대응 절차서), 각종 산출물 문서</t>
+        </is>
+      </c>
+      <c r="V8" s="19" t="inlineStr">
+        <is>
+          <t>국가를 당사자로 하는 계약에 관한 법률 및 시행령/시행규칙, 협상에 의한 계약체결기준, 소프트웨어 진흥법 제48조, 중소기업기본법, 소상공인 보호 및 지원에 관한 법률, 중소기업제품 구매촉진 및 판로지원에 관한 법률, 소프트웨어 기술성 평가기준 지침, 개인정보보호법, 정보통신망 이용촉진 및 정보보호 등에 관한 법률, 행정업무의 효율적 운영에 관한 규정, 공공기관의 기록물관리에 관한 법률, 행정기관 및 공공기관 정보시스템 구축·운영 지침, 소프트웨어 개발보안 가이드, 웹응용프로그램 개발보안 가이드, 전자정부서비스 호환성 준수지침, 표준개인정보보호지침, 웹 접근성 향상을 위한 국가표준 기술 가이드라인, 한국형 웹 콘텐츠 접근성 지침 2.1, 개인정보의 안전성 확보조치 기준, 소프트웨어사업 요구사항 분석적용 가이드, W3C 웹표준, OWASP TOP 10, 국정원 8대 취약점, 용역계약일반조건 제56조</t>
+        </is>
+      </c>
+      <c r="W8" s="19" t="inlineStr">
+        <is>
+          <t>부천대학교가 운영 중인 기존 그룹웨어 시스템은 성능 및 운용 개선에 한계가 있어 급변하는 경영환경과 정보관리 변화에 효율적으로 대응하지 못하고 있다. 노후화된 시스템으로 서비스 안정성이 저하되고, 최신 업무 트렌드(AI·모바일·반응형 웹·비대면 협업)를 반영하지 못해 업무 효율성이 떨어지는 상황이다.</t>
+        </is>
+      </c>
+      <c r="X8" s="19" t="inlineStr">
+        <is>
+          <t>ActiveX 등 비표준 기술 의존, 제한된 브라우저 지원, 고정형 UI, 업무편람의 오프라인·종이 중심 관리, AI·모바일 연계 기능 부재, 전자결재·메일·게시판·기록물이 분리 운영되어 사용자 편의성 저하, 데이터 마이그레이션·커스터마이징 기능 이관 어려움, 서버 인프라 노후화로 인한 확장성·안정성 부족.</t>
+        </is>
+      </c>
+      <c r="Y8" s="19" t="inlineStr">
+        <is>
+          <t>HTML5 기반 반응형·크로스브라우징 그룹웨어로 재구축되어 500명 이상 사용자가 Edge·Chrome·Safari·Firefox 등 다양한 환경에서 사용 가능. 개인화 포털·포틀릿 Drag&amp;Drop, 통합인증(SSO 8식)·통합검색·통합알림 제공. 전자결재는 한글 웹/폼 기안기, 연동결재·기록물 관리·문서수발신 자동화. 생성형 AI(ChatGPT·Gemini), RAG 기반 검색, AI Agent(MCP)로 일정·자원 자동예약, AI 기안·요약·번역·음성인식 지원. 모바일 생체인증, CalDAV 동기화, 업무편람 온라인화, 협업 공간(팀룸)·프로젝트·위키·메신저 통합으로 비대면 협업과 업무 연속성 확보.</t>
+        </is>
+      </c>
+      <c r="Z8" s="19" t="inlineStr">
+        <is>
+          <t>조직도·사용자·개인정보·직위·직급, 기존 게시판·전자결재 문서함 본문·첨부파일, 전자우편·주소록, 업무협조 데이터를 신규 시스템으로 마이그레이션. 결재 문서 데이터의 구조화(DB화)를 통해 사용자 정의 문서함·타 시스템 연동·통계 활용. 접속로그·사용자 통계·배치 모니터링 로그를 시스템 관리에 활용.</t>
+        </is>
+      </c>
+      <c r="AA8" s="19" t="inlineStr">
+        <is>
+          <t>1) 지자체·공공기관 그룹웨어에 RAG 기반 AI 검색·요약을 접목하여 내부 규정·매뉴얼 Q&amp;A 봇으로 활용
+2) 공공기관 회의실·차량·장비 예약 시스템에 AI Agent(MCP) 기반 자동 예약·일정 조율 기능 적용
+3) 전자결재·기록물 관리가 필요한 중앙부처·공단의 문서 수발신 시스템에 생성형 AI 기안·요약·맞춤법 검사 기능 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="400" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>RFP-007</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>(혁신) 삼육대학교 AI기반 통합업무포털 구축 및 개발 멘토링</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>삼육대학교</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>기획처 AI대학혁신센터</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>미기재</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>제한경쟁입찰(협상에 의한 계약)</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="L9" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="M9" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="19" t="inlineStr">
+        <is>
+          <t>소프트웨어사업자(소프트웨어산업진흥법), 직접생산증명서(중소기업 진흥 및 제품구매 촉진에 관한 법률)</t>
+        </is>
+      </c>
+      <c r="O9" s="19" t="inlineStr">
+        <is>
+          <t>시스템구축</t>
+        </is>
+      </c>
+      <c r="P9" s="19" t="inlineStr">
+        <is>
+          <t>행정·학사·위원회 업무 통합포털, 문서 자동생성, 행정위원회 의안(안건) 관리</t>
+        </is>
+      </c>
+      <c r="Q9" s="19" t="inlineStr">
+        <is>
+          <t>LLM, OpenAI ChatGPT, Anthropic Claude, Structured Output(JSON Schema), RAG, 벡터DB, PII 마스킹, Prompt/Response 필터링, Moderation, AI Agent</t>
+        </is>
+      </c>
+      <c r="R9" s="19" t="inlineStr">
+        <is>
+          <t>업무/사업 정의서 기반 기안서·공문·이메일·완료보고서·회의자료 초안 자동 생성, 행정위원회 의안 초안 작성·검수·요약, 규정·지침·과거 의안 RAG 기반 참조, 정책·금칙어·PII 검수, 문서 포맷 자동 변환을 통한 업무 자동화 및 데이터 기반 의사결정 지원</t>
+        </is>
+      </c>
+      <c r="S9" s="19" t="inlineStr">
+        <is>
+          <t>【기능】 FUR-001 역할별 로그인 및 SSO 연동 / FUR-002 JWT/세션 기반 인증 관리 / FUR-003 사용자 프로필 관리 / FUR-004 역할 기반 접근제어(RBAC) / FUR-005 업무/사업 정의서 등록·조회 / FUR-006 정의서 템플릿 관리 / FUR-007 정의서 검증 및 승인 워크플로 / FUR-008 정의서 버전 관리 / FUR-009 정의서 기반 기안서 자동 생성 / FUR-010 정의서 기반 공문 초안 자동 생성 / FUR-011 정의서 기반 이메일 초안 자동 생성 / FUR-012 정의서 기반 완료보고서 자동 생성 / FUR-013 문서 템플릿 관리 / FUR-014 자동 생성 문서 재생성·수정 및 이력 관리 / FUR-015 표준어/금칙어 정책 검수 / FUR-016 필수 항목·형식 스키마 검증 / FUR-017 메타데이터 동기화 / FUR-018 전자결재 기안/공문 초안 Push 연동 / FUR-019 메일 시스템(SMTP) 연동 / FUR-020 알림(SU-TALK·이메일) 발송 관리 / FUR-021 행정위원회 회차/회의 일정 관리 / FUR-022 의안 등록 및 AI 초안 작성 / FUR-023 의안 검토·승인 및 버전 관리 / FUR-024 의안 뷰어(본문·첨부·데이터 패널) / FUR-025 행정위원회 전자투표 / FUR-026 의결 결과 요약 및 후속보고 자동 생성 / FUR-027 의안별 예산 현황 및 집행 가능액 조회 / FUR-028 의안별 업체 수행 이력·평가 조회 / FUR-029 위원 사전 열람 및 댓글·의견 수렴 / FUR-030 위원장 상정 승인/반려 처리 / FUR-031 감사로그 관리 / FUR-032 AI 템플릿/프롬프트/스키마 관리 / FUR-033 모델별 호출 설정 및 전환(GPT/Claude) / FUR-034 RAG(벡터DB) 기반 참조 문서 / FUR-035 AI 응답 정책 검수 및 PII 마스킹 / FUR-036 업무/프로젝트 진행 현황 대시보드 / FUR-037 의안·의결 현황 대시보드 / FUR-038 사용자·역할·권한 관리 / FUR-039 시스템 환경설정 관리 / FUR-040 로그·통계·AI 사용량 모니터링
+【성능】 PER-001 일반 화면 응답 시간(3초 이내) / PER-002 주요 API 평균 응답 시간(1000ms 이내) / PER-003 동시 사용자·피크 트래픽 처리 / PER-004 대량 문서 생성·배치 작업 처리 시간
+【데이터】 DAR-001 데이터 모델 및 참조 무결성 / DAR-002 이력/버전 데이터 관리 / DAR-003 정기 백업 및 재해 복구 / DAR-004 로그·감사 데이터 수집·보존 / DAR-005 개인정보·민감정보 마스킹/익명화
+【보안】 SER-001 인증·인가·계정잠금·비밀번호 정책 / SER-002 대학 SSO 연동 및 역할 매핑 / SER-003 전송 구간 암호화(TLS) / SER-004 DB·파일 저장 암호화 및 접근 통제 / SER-005 전자투표 위변조 방지 / SER-006 정기 취약점 진단 및 보안 패치
+【기획/UIUX멘토링】 DER-001 초기 기획 정리 및 화면 디자인·와이어프레임 / DER-002 프론트엔드 개발 진행 / DER-003 학습공동체(CoP) 제작 주제·범위 공동 기획 / DER-004 CoP 개발 부분 기획·화면 디자인 멘토링
+【품질】 QUR-001 시스템 가용성·장애율 / QUR-002 테스트 커버리지·결함 밀도 / QUR-003 기술 문서화 품질 / QUR-004 UI/UX 및 접근성 품질
+【제약】 COR-001 기본 기술 스택 준수/대체 조건 / COR-002 기존 시스템 연동 방식 준수 / COR-003 사업 추진 일정·마일스톤 준수 / COR-004 오픈소스 라이선스 및 상용 SW 사용 제약
+【프로젝트관리】 PMR-001 프로젝트 조직 구성 및 R&amp;R / PMR-002 WBS 기반 일정·진도 관리 / PMR-003 주간/월간 회의·보고 체계 / PMR-004 형상관리(Git) 전략 / PMR-005 이슈·리스크 관리 / PMR-006 단계별 산출물 검수·인수
+【프로젝트지원】 PSR-001 내부 개발자 기술 교육 / PSR-002 바이브 코딩 멘토링·코드 리뷰 / PSR-003 오픈 후 초기 안정화 및 운영 지원(3개월 이상) / PSR-004 운영자·사용자 매뉴얼 및 교육 자료 제공</t>
+        </is>
+      </c>
+      <c r="T9" s="19" t="inlineStr">
+        <is>
+          <t>FUR-001 역할별 로그인·SSO 연동: 대학 SSO와 연동한 단일 로그인, 소속·직책·이메일 자동 수신, 내부 관리자 전용 계정, 역할(기안자·검토자·위원·위원장·기획팀·관리자)별 메뉴 접근 제한, 로그인 실패·세션 만료 오류 처리, 비정상 IP 보안 알림, 세션/토큰 유효기간 및 재발급.
+FUR-002 JWT 기반 인증: Access/Refresh 토큰 또는 세션 발급, 서명·만료 검증, API 호출 시 유효성 검사, 로그아웃 시 토큰 무효화, 블랙리스트, Refresh 갱신, 에러 코드 분리.
+FUR-003 사용자 프로필: 이름·소속·직책·연락처 조회, 개인화 context 관리, 형식 검증, 프로필 사진, 변경 이력, 역할·권한 변경은 관리자 전용.
+FUR-004 RBAC: 역할 정의, 메뉴·기능 단위 권한(조회/등록/수정/삭제), 메뉴 자동 필터링, 권한 없는 기능 차단, 즉시 반영, Row-Level 권한.
+FUR-005 정의서 등록·조회: 제목·목적·배경·기간·예산·담당부서 필드, JSON Schema 기반 동적 필드, 목록·상세 조회, 부서/기간/상태 필터, 임시저장·최종 저장.
+FUR-006 정의서 템플릿 관리: 업무 유형·부서별 템플릿 CRUD, 필수/옵션 항목, 템플릿별 JSON Schema, 미리보기, 변경 이력.
+FUR-007 검증 및 승인 워크플로: 상태값(작성중·검토중·승인·반려), 승인·반려 처리, 반려 사유 필수, 승인자 지정, 이력 기록, 승인 완료 후 수정 제한.
+FUR-008 버전 관리: V1 자동 생성, 수정 시 버전 증가, 버전별 조회, Diff 비교, 권한자 롤백.
+FUR-009 기안서 자동 생성: 정의서 기반, 목적·예산·기간·추진내용 자동 매핑, 부서·결재선 자동 채움, 편집·재생성, 버전 관리, PDF/DOCX 출력.
+FUR-010 공문 초안 자동 생성: 대내/대외 선택, 수신처·참조·제목·본문 자동 생성, 기관 표준 양식, 편집, PDF/DOCX 출력, 공문 번호는 기존 전자결재 시스템에서 부여.
+FUR-011 이메일 초안 자동 생성: 안내/협조/보고 유형, 제목·본문·인사말·맺음말 자동 생성, 수신자 자동완성, 편집, SMTP 연동 발송, 발송 이력.
+FUR-012 완료보고서 자동 생성: 템플릿 관리, 목표·KPI·예산과 수행 결과·집행 실적 자동 매핑, AI 요약 기반 성과·향후 과제, 편집, PDF/DOCX 출력, 버전 관리.
+FUR-013 문서 템플릿 관리: 기안·공문·메일·보고서 템플릿 CRUD, 부서별 전용, 변수(${부서명}, ${예산}) 정의, 미리보기·테스트, 변경 이력 및 롤백.
+FUR-014 자동 생성 문서 재생성·수정: 편집 화면, 정의서 변경 시 재생성 선택, 수정 내용 유지/초기화, 버전 저장·비교, 최종 제출 버전 잠금.
+FUR-015 표준어/금칙어 정책 검수: 금칙어 CRUD, 저장·제출 시 자동 검수, 위반 위치 표시·수정 제안, 결과 요약, 로그 저장.
+FUR-016 스키마 검증: JSON Schema 기반 필수 항목, 저장 시 누락 검증, 데이터 타입·길이·형식 검증, 실패 항목 안내.
+FUR-017 메타데이터 동기화: 외부 시스템 API로 조직·사용자·양식 코드 조회, 정기 스케줄 동기화, 신규·변경·삭제 로직, 결과 로그·오류 알림, 자동완성 구성.
+FUR-018 전자결재 Push 연동: API 호출, 기안/공문 초안 본문·제목·첨부 전송, 성공/실패 수신·상태 갱신, 중복 전송 방지, 문서번호·URL 역참조.
+FUR-019 메일 시스템 연동: SMTP/메일 게이트웨이 설정, 발신·수신·제목·본문·첨부 발송, 성공/실패 기록·재발송, 발송 이력, 속도 제어.
+FUR-020 알림 발송 관리: 주요 이벤트(승인요청·상정·투표시작·의결완료) 알림, SU-TALK·이메일·SMS 채널, 이벤트별 템플릿, 실패 재시도·관리자 알림, 수신 여부 사용자 설정.
+FUR-021 회차/회의 일정 관리: 위원회별 회차 CRUD, 일시·장소·주요 안건 요약, 그룹웨어 캘린더 연동, 회차별 안건 목록, 일정 변경 알림.
+FUR-022 의안 등록 및 AI 초안 작성: 안건명·제안부서·제안자·목적·배경·예산 입력, AI 초안 생성 버튼, 초안 편집·재생성, 안건 유형 분류, 임시저장·제출.
+FUR-023 의안 검토·승인 및 버전 관리: 담당자·기획팀·위원장 검토 단계, 승인·반려·사유 입력, 코멘트, 버전 증가·비교, 상태를 '상정 승인' 등으로 변경.
+FUR-024 의안 뷰어: 본문 뷰어, 첨부자료 미리보기, 예산 현황 패널(예산·집행·잔액), 업체 수행 이력·평가 패널, 관련 규정 링크, Zoom 화상회의 플로팅.
+FUR-025 전자투표: 찬성/반대/보류 선택, 1인 1표·중복투표 방지, 투표 기간 설정·제어, 실시간 집계.
+FUR-026 의결 결과 요약 및 후속보고: 투표 결과 자동 집계, 회의 기록(메모·전사본) AI 요약, 결정사항 문구 자동 생성, 후속조치(담당부서·기한·업무) 구성, 후속보고서 편집·출력.
+FUR-027 예산 현황 조회: 예산 코드·과목 선택/자동 매핑, 예산액·집행액·잔액 조회, 집행 예정액 입력 시 집행 가능 계산, 예산 시스템 API 연동.
+FUR-028 업체 수행 이력·평가: 업체 검색 또는 자동 표시, 계약·수행 이력, 평가 점수·등급, 시각화, 계약/구매 시스템 API 연동.
+FUR-029 사전 열람·댓글: 위원용 의안 목록·상세, 댓글 CRUD, 멘션, 알림, 비공개 댓글(위원장·기획팀 전용).
+FUR-030 위원장 상정 승인/반려: 위원장 전용 화면, 반려 사유 필수, 승인 시 회차·상정 순서 지정, 상태 반영, 로그·알림.
+FUR-031 감사로그 관리: 등록/수정/승인/투표/의결 행위 로그, 사용자·시간·IP·대상·변경내용 기록, 기간·사용자·의안별 검색, 감사 권한자만 열람, Write-once·해시.
+FUR-032 AI 템플릿/프롬프트/스키마 관리: 프롬프트 템플릿 CRUD, 문서 유형·단계별 분리, Structured Output 스키마 관리, 테스트 호출 미리보기, 변경 이력.
+FUR-033 모델 호출 설정·전환: GPT/Claude API Key·모델명 설정, 기능별 기본 모델 지정, 장애·비용 시 대체 모델 전환, 호출 제한(토큰·월 사용량), 사용 통계.
+FUR-034 RAG 벡터DB: 참조 문서(PDF·DOCX·TXT) 업로드, 분할·임베딩·벡터DB 저장, 키워드·유사도 검색, 의안/정의서에 참조 문서 연결, 수정 시 재임베딩.
+FUR-035 AI 응답 검수·PII 마스킹: PII(전화번호·계좌번호) 탐지, 금칙어·부적절 표현 검출, 자동 마스킹, 정책 위반 응답 경고·재생성, 검수 로그.
+FUR-036 업무/프로젝트 대시보드: 상태별 건수, 부서·기간·유형 필터, 예산 집행률·기한 경과 요약, 경고 상태 강조, 상세 화면 이동.
+FUR-037 의안·의결 대시보드: 회차·위원회별 현황, 찬성/반대/보류 비율 그래프, 부서별 상정·채택 비율, 월/분기/연도 추이, 장기 계류 목록.
+FUR-038 사용자·역할·권한 관리: 사용자 목록·검색, 역할 부여/변경/회수, 역할 CRUD, 역할별 권한 설정, 계정 잠금/해제.
+FUR-039 시스템 환경설정: 외부 API URL·토큰, AI 모델 API Key·파라미터, 메일/알림 연동 설정, 변경 이력·롤백, 유효성 검증.
+FUR-040 로그·통계·AI 사용량 모니터링: 접속·오류·API 로그, AI 호출 건수·성공률·응답시간, 토큰 사용량·비용 추정, 사용자·부서별 통계, 필터·CSV 내보내기.
+PER-001 화면 응답시간: 주요 일반 화면 3초 이내, 목록 20~50건 기준, 대시보드 Lazy Loading, APM 연동.
+PER-002 API 응답시간: 핵심 API 평균 1000ms 이내(목표 300ms), 외부 API 타임아웃·재시도, 레이턴시·에러율 모니터링.
+PER-003 동시 사용자: 수백 명 수준 수용, Load/Stress Test, 스케일업/아웃, 큐잉 등 완화 정책.
+PER-004 대량 배치: N건당 M분 이내 목표, 야간·저부하 시간대 실행, 진행률 표시, 실패 재시도·부분 재처리.
+DAR-001 데이터 모델: ERD, FK 참조 무결성, CASCADE/RESTRICT, 공통 코드 분리, 3차 정규형, Soft Delete, 마이그레이션 전략.
+DAR-002 이력/버전: 정의서·문서·의안별 버전 테이블, V1 자동 생성, 수정 시 버전 증가·시점·사용자 기록, Diff 비교, 권한자 롤백.
+DAR-003 백업/복구: 일 단위 전체 백업+증분, 암호화 저장, 1년 이상 보관, RTO/RPO 설정, 모의 복구 테스트.
+DAR-004 로그·감사 보존: 서비스·오류·감사 로그 분리, 일반 3년/보안 5년 보존, 기간·유형·사용자 검색, 접근 권한 제한, 압축·아카이빙.
+DAR-005 개인정보·민감정보 마스킹: 개인정보 항목 정의, AES 암호화, 화면 마스킹(010-****-1234), 로그 익명화, 처리 이력 로깅, AI 호출 시 필터링.
+SER-001 인증·인가·계정잠금: 비밀번호 구성 규칙·변경 주기·재사용 제한, 로그인 실패 잠금, 해제 절차, 권한 부여/회수, 감사로그.
+SER-002 SSO 연동: SSO 보호·보안 옵션, Assertion/Token 위변조 방지, 신뢰 수준, 그룹/속성 역할 매핑, 장애 시 대체 로그인, 연동 로그 보관.
+SER-003 전송 구간 암호화: HTTPS(TLS), 외부 API TLS·인증서 검증, 방화벽/ACL, CORS 허용 도메인, 내부망/외부망·DMZ, 의심 트래픽 탐지·차단.
+SER-004 저장 암호화·접근 통제: DB 민감 컬럼 AES 암호화, DB 계정 최소권한, 파일 저장소 접근 통제, Presigned URL, 접근 로그, 백업 암호화.
+SER-005 전자투표 위변조 방지: 투표 데이터 해시/서명, Write-once/Append-only, 집계 로직 무결성, 투표 로그 보존, 조회 권한 범위.
+SER-006 정기 취약점 진단: 웹·서버·DB 정기 점검, OWASP Top10, 긴급/보통/경미 등급별 대응, 패치 절차(개발/검증/운영), 보고서, 외부 점검 대응.
+DER-001 초기 기획·화면 디자인·와이어프레임: 핵심 영역 기획, 핵심·확장 범위 설정, 세부 페이지/기능 기획, 핵심 기능 화면 디자인·와이어프레임.
+DER-002 프론트엔드 개발: 도출된 디자인·와이어프레임 기반 코딩, 확정된 스택 기반 개발, 백엔드 연결, 업무 흐름별 테스트.
+DER-003 CoP 공동 기획: CoP 주중 정기 모임(17:30~20:30 주 2회) 멘토링, 모듈형 세부 업무 시스템 공동 기획, 보안 요소 컨설팅.
+DER-004 CoP 개발 멘토링: 개발 방법 컨설팅, 일관된 UI/UX 디자인 멘토링, 템플릿 기반 개발 가이드, 정기 모임 개발 멘토링, 바이브코더용 디자인 가이드 제작.
+QUR-001 가용성·장애율: 연간/월간 가동률 99.5% 이상, 계획 정지/장애 정지 구분, 등급별 허용 시간, 대응·복구 시간 목표, 통계 보고 주기.
+QUR-002 테스트 커버리지·결함 밀도: 단위·통합 커버리지 50% 이상, 결함 밀도 기준, 테스트 유형·범위, 결과 보고서, 릴리즈 전 필수 테스트.
+QUR-003 기술 문서화: 아키텍처·테이블·API 명세·운영 매뉴얼, 템플릿 형식, 최신성 유지, 상세도 요구, 산출물 검수 품질 평가.
+QUR-004 UI/UX·접근성: PC·태블릿·모바일 반응형, 공통 UX 패턴, 글자·색상·여백, 색각보정·대체 텍스트, 오류·로딩 안내.
+COR-001 기술 스택: Next.js/NestJS/PostgreSQL 명시, 대체 제안 시 성능·보안·유지보수·교육 비교자료, 인프라·보안 호환성, 내부 개발자 습득 가능성.
+COR-002 연동 방식 준수: 연동 대상·API 목록 명시, Push/Pull·호출 주기·데이터 범위 가이드 준수, 전자결재·공문은 초안 Push까지만 허용, 실패 시 재시도·알림.
+COR-003 일정·마일스톤: 착수~MVP~정식오픈 일정 준수, 단계별 마일스톤, 지연 시 사전 통보·협의, 중간 성과 점검 회의, 위반 시 조정·패널티·보완.
+COR-004 라이선스: 사용 가능 오픈소스(MIT·Apache 2.0), GPL 등 전이 라이선스 사전 승인, 상용 SW·API 비용, 외부 서비스 장애 대체, 라이브러리 목록·버전 명세.
+PMR-001 조직 구성: 발주기관·수행사·협력사 조직도, PO/PM/개발자/디자이너/QA/운영 역할, R&amp;R·의사결정 권한, 단일 연락 창구.
+PMR-002 WBS·진도 관리: WBS 수립, 단계·작업별 시작·완료·담당자·산출물, 간트 차트, 주간·월간 진도율, 지연·리스크 보고·조정.
+PMR-003 회의·보고 체계: 주간 실무·월간 진행 보고, 참석자·안건·회의록, 결정사항·To-Do 공유, 긴급 이슈 비정기 회의, 협업 도구.
+PMR-004 형상관리: Git 도구, Git Flow/Trunk 기반 브랜치 전략, 환경별 브랜치, 코드 리뷰·머지 승인, Blue-Green/Rolling 배포, 롤백 절차.
+PMR-005 이슈·리스크: 항목(내용·심각도·영향도·상태), 등록·분류·우선순위, 주요 리스크(일정·인력·기술·연동) 대응 전략, 정기 보고.
+PMR-006 산출물 검수·인수: 단계별 필수 산출물(기획·설계·개발·테스트·교육), 제출 시기·형식, 검수 기준(기능·성능·보안·문서), 승인/보완/반려 조치, 인수조건·하자보수.
+PSR-001 내부 개발자 교육: 교내 학습공동체 대상, Next.js/NestJS/PostgreSQL·아키텍처·운영 교육, 집체/워크숍/실습, 자료 제공, 사전/사후 점검.
+PSR-002 바이브 코딩 멘토링: 참여 범위, 시니어 개발자 멘토 투입, 코드 리뷰 프로세스, 페어 프로그래밍·워크숍, 유지보수 가능 수준 문서·가이드.
+PSR-003 오픈 후 안정화: 최소 3개월 이상 초기 안정화, 장애 응답·복구 SLA, 무상 보완 범위, 문의 대응 채널, 초기 데이터 기반 튜닝.
+PSR-004 매뉴얼 및 교육: 운영자 매뉴얼(계정·권한·환경설정·모니터링), 사용자 매뉴얼, 포맷(PDF·온라인), 교육 자료, 릴리즈 시 매뉴얼 갱신.</t>
+        </is>
+      </c>
+      <c r="U9" s="19" t="inlineStr">
+        <is>
+          <t>AION 통합업무포털 및 행정위원회 의안 관리 모듈 소스코드, HLD/LLD 설계서, API 명세서, 테이블 정의서, 운영 매뉴얼, 사용자/관리자/개발자 매뉴얼, 교육 자료(슬라이드·데모 시나리오), 개발 표준·가이드 문서, 디자인 가이드·템플릿, WBS·추진일정, 테스트 계획서·결과서, 보안 취약점 점검 보고서, 멘토링·코드 리뷰 기록, 백업/복구 매뉴얼</t>
+        </is>
+      </c>
+      <c r="V9" s="19" t="inlineStr">
+        <is>
+          <t>국가를 당사자로 하는 계약에 관한 법률 및 시행령 제12조·제43조·제76조, 소프트웨어산업진흥법, 중소기업 진흥 및 제품구매 촉진에 관한 법률, 개인정보보호법, OWASP Top10</t>
+        </is>
+      </c>
+      <c r="W9" s="19" t="inlineStr">
+        <is>
+          <t>삼육대학교는 행정·학사·위원회 관련 문서와 업무가 부서별·시스템별로 분산되어 있고, 문서 형식 불일치·반복 입력·수작업 검토로 인해 동일 내용을 여러 서식에 반복 작성하고 문서 간 핵심값(예산·기간·대상)이 불일치하거나 누락되는 문제가 발생. 특히 행정위원회 의안의 사전 검토·의견 수렴·투표 결과 정리가 수작업으로 처리되고 담당자 개인 역량에 따라 업무 품질 편차가 큰 상황.</t>
+        </is>
+      </c>
+      <c r="X9" s="19" t="inlineStr">
+        <is>
+          <t>동일/유사 내용을 기안·공문·메일·보고서 등 N개 서식에 반복 작성, 문서 간 핵심값 불일치·누락, 행정위원회 의안의 기안→검토→상정→심의→의결→후속조치가 수작업·오프라인 중심으로 처리, 예산·업체 이력·규정 등이 의사결정 시점에 통합 제공되지 않음, 부서·시스템 단위 문서 관리로 프로젝트 단위 통합 관리 부재, 내부 개발 역량 축적 기반 부족.</t>
+        </is>
+      </c>
+      <c r="Y9" s="19" t="inlineStr">
+        <is>
+          <t>업무 중심(Work-Centric)으로 정의된 '계획·의안·업무정의서'를 기반으로 한 번의 계획 작성으로 기안서·공문·이메일·완료보고서·회의자료 초안이 자동 생성되는 AION 통합업무포털 구축. 행정위원회 의안의 초안 작성→검토 승인→상정 공지→사전 열람/댓글→전자투표→의결/후속조치 전 과정이 전자프로세스+AI 기반으로 통합되고, 예산·업체 이력·규정 데이터 패널을 통해 데이터 기반 의사결정 지원. GPT/Claude 기반 문서 초안·검수·요약, RAG 벡터DB 기반 참조, PII 마스킹·정책 검수 가드레일 적용. 수행사는 코어 모듈·아키텍처·디자인 가이드를 구축하고 교내 바이브 코딩 팀이 세부 기능을 직접 개발하도록 멘토링·코드 리뷰·교육을 제공하여 장기적 내부 개발 역량 강화.</t>
+        </is>
+      </c>
+      <c r="Z9" s="19" t="inlineStr">
+        <is>
+          <t>업무/사업 정의서(JSON Schema 구조화 데이터), 행정위원회 의안·투표·의결 기록, 예산 현황·집행액(예산 시스템 API), 업체 계약·수행 이력·평가(계약/구매 시스템 API), 조직·사용자·양식 코드 메타데이터(그룹웨어·학사·전자결재 연동), 규정·지침·과거 의안 문서를 임베딩하여 벡터DB에 저장해 RAG 컨텍스트로 활용, 감사로그·AI 호출 로그를 통계·모니터링에 활용.</t>
+        </is>
+      </c>
+      <c r="AA9" s="19" t="inlineStr">
+        <is>
+          <t>1) 중앙부처·지자체의 위원회 안건 관리에 전자투표·AI 의안 초안·예산/업체 데이터 패널을 도입하여 위원회 운영 전 과정을 디지털화
+2) 공공기관의 사업계획서·기안·공문·완료보고서 자동 생성 파이프라인을 구축하여 '한 번의 계획, N개 문서' 방식으로 행정 문서 작업 절감
+3) 대학·연구기관 내부 규정·매뉴얼·과거 문서를 벡터DB로 구축하고 PII 마스킹·정책 검수 가드레일을 적용한 안전한 생성형 AI 업무 어시스턴트로 확장</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:AA7"/>
   <mergeCells count="6">
